--- a/resultados/terraroxa/inventario_links.xlsx
+++ b/resultados/terraroxa/inventario_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,181 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;ajaxPrevent=1581348377296&amp;file=7EAAA743718582070E959CBEE7C2B036C2AE84AC&amp;sistema=WPO&amp;classe=UploadMidia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>terraroxa.atende.net</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>200</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:09:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;ajaxPrevent=1581348399199&amp;file=C359F4297DFEFF4C8E323F58204B88B20120F731&amp;sistema=WPO&amp;classe=UploadMidia</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>terraroxa.atende.net</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>200</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:09:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;ajaxPrevent=1581348418992&amp;file=2DCDF1DD2C6BA0351CE38B1C75A4A3800C01DF90&amp;sistema=WPO&amp;classe=UploadMidia</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>terraroxa.atende.net</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>200</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:09:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;ajaxPrevent=1581348435782&amp;file=46D198977397730583BBB3110B198CE4D2D90B70&amp;sistema=WPO&amp;classe=UploadMidia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>terraroxa.atende.net</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>200</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:09:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.terraroxa.pr.gov.br/autoatendimento/servicos/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=798929CCFE972E7606B660D31A4770D1026AF7B7&amp;sistema=WPO&amp;classe=UploadMidia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>www.terraroxa.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>200</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:10:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/terraroxa/inventario_links.xlsx
+++ b/resultados/terraroxa/inventario_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,6 +1268,41 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>terraroxa</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://terraroxa.atende.net/autoatendimento/servicos/atende.php?rot=1&amp;aca=119&amp;ajax=t&amp;processo=viewFile&amp;file=798929CCFE972E7606B660D31A4770D1026AF7B7&amp;sistema=WPO&amp;classe=UploadMidia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>terraroxa.atende.net</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>200</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-11 11:44:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/terraroxa/inventario_links.xlsx
+++ b/resultados/terraroxa/inventario_links.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
